--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-02-09T14:15:30.453917</t>
+          <t>2026-02-16T13:13:53.983017</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -645,7 +645,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -817,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-02-09T11:25:08.384717</t>
+          <t>2026-03-03T15:30:15.413063</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2587,7 +2587,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EMSR820</t>
+          <t>EMSR821</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wildfire in East Attica, Greece</t>
+          <t>Wildfire in Peloponnese, Greece</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>POINT (23.802395 38.169519)</t>
+          <t>POINT (21.790352 37.231148)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2025-07-28T13:24:34.744611</t>
+          <t>2025-07-28T15:11:33.550671</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2632,11 +2632,11 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>On the 26 July 2025 at 18:24 (CET), a wildfire was reported to have affected the area near Krioneri, in the outskirts of Athens, Greece. The fire expanded rapidly; residents of Krioneri and Drosopigi had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces...</t>
+          <t>On the 26 July 2025 at 15:08 (CET), a wildfire was reported to have affected the area very close to Aetos in Peloponnese Region, Greece. The fire expanded rapidly; residents of Aetos and Monastiri had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces an...</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EMSR821</t>
+          <t>EMSR820</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wildfire in Peloponnese, Greece</t>
+          <t>Wildfire in East Attica, Greece</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>POINT (21.790352 37.231148)</t>
+          <t>POINT (23.802395 38.169519)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-07-28T15:11:33.550671</t>
+          <t>2025-07-28T13:24:34.744611</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2689,11 +2689,11 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>On the 26 July 2025 at 15:08 (CET), a wildfire was reported to have affected the area very close to Aetos in Peloponnese Region, Greece. The fire expanded rapidly; residents of Aetos and Monastiri had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces an...</t>
+          <t>On the 26 July 2025 at 18:24 (CET), a wildfire was reported to have affected the area near Krioneri, in the outskirts of Athens, Greece. The fire expanded rapidly; residents of Krioneri and Drosopigi had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces...</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -21816,7 +21816,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>EMSN110</t>
+          <t>EMSN109</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -21831,12 +21831,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Wildfire in Alburquerque, Spain</t>
+          <t>Wildfire in Alcaracejos, Spain</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>POINT (-6.85472 40.02093)</t>
+          <t>POINT (-4.94932 38.2282)</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -21866,14 +21866,14 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>EMSN108</t>
+          <t>EMSN110</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -21888,12 +21888,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Wildfire in San Felices de los Gallegos, Spain</t>
+          <t>Wildfire in Alburquerque, Spain</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>POINT (-6.67526 40.8026)</t>
+          <t>POINT (-6.85472 40.02093)</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -21918,19 +21918,19 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>EMSN109</t>
+          <t>EMSN108</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -21945,12 +21945,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Wildfire in Alcaracejos, Spain</t>
+          <t>Wildfire in San Felices de los Gallegos, Spain</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>POINT (-4.94932 38.2282)</t>
+          <t>POINT (-6.67526 40.8026)</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -21975,12 +21975,12 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -23304,27 +23304,27 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>EMSN102</t>
+          <t>EMSN103</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Spain'}]</t>
+          <t>[{'short_name': 'Central African Republic'}]</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Wildfires in Huelva, Spain</t>
+          <t>IDP camp monitoring in Bria, Central African Republic</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>POINT (-6.61875 37.43943)</t>
+          <t>POINT (21.9657 6.54857)</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -23345,43 +23345,43 @@
         <v>1</v>
       </c>
       <c r="K415" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d P19-Population displacement location P19-MONIT01-Overview Map P19-Overview Map P19-Population displacement location-MONIT01</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>EMSN103</t>
+          <t>EMSN102</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Central African Republic'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>IDP camp monitoring in Bria, Central African Republic</t>
+          <t>Wildfires in Huelva, Spain</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>POINT (21.9657 6.54857)</t>
+          <t>POINT (-6.61875 37.43943)</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -23402,16 +23402,16 @@
         <v>1</v>
       </c>
       <c r="K416" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d P19-Population displacement location P19-MONIT01-Overview Map P19-Overview Map P19-Population displacement location-MONIT01</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -27153,7 +27153,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>POINT (-5.5651 40.0425)</t>
+          <t>POINT (-5.565099999999999 40.04249999999998)</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -27161,7 +27161,11 @@
           <t>2020-10-22T14:45:00</t>
         </is>
       </c>
-      <c r="G481" t="inlineStr"/>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>2026-03-05T13:11:19.243588</t>
+        </is>
+      </c>
       <c r="H481" t="inlineStr">
         <is>
           <t>response</t>
@@ -27178,7 +27182,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>Last summer a great fire broke out in the mountains of the north of the C√°ceres department, tributaries that pour their waters into the Tietar river spring from the affected mountains. Also, on the 20th and 21st of October 2020, the same area has received heavier rainfall than usual during a sho...</t>
+          <t>Last summer a great fire broke out in the mountains of the north of the Caceres department, tributaries that pour their waters into the Tietar river spring from the affected mountains. Also, on the 20th and 21st of October 2020, the same area has received heavier rainfall than usual during a ...</t>
         </is>
       </c>
       <c r="M481" t="inlineStr"/>
@@ -29920,115 +29924,115 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
+          <t>EMSN066</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Iran'}]</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Flood delineation and flood damage assessment, Iran</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>POINT (58.96228 25.99307)</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2020-04-09T01:00:00</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I530" t="b">
+        <v>1</v>
+      </c>
+      <c r="J530" t="n">
+        <v>3</v>
+      </c>
+      <c r="K530" t="n">
+        <v>11</v>
+      </c>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>The scope of the service request EMSN-066 is to delineate the extent and assess damage of 9 to 11 January 2020 flood event, in South-East Iran. As predicted by Copernicus EMS service GloFAS, days of heavy rain from 9 to 11 January 2020 caused severe flooding in southern Iran, in Sistan and Baluchestan, Hormozgan and south of Kerman provinces. Flooding has blocked roads and damaged houses, bridges, crops and infrastructure. Dozens of areas have been left isolated after roads were damaged or block Reservoir and dam change detection (Overview A3) Reference map (Overview A3) Flood delineation (Overview A3) Damage assessment (Overview A3) Reference map (Overview A2) Flood delineation (Overview A2) Damage assessment (Overview A2) Reservoir and dam change detection (Overview A1) Reference map (Overview A1) Flood delineation (Overview A1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
           <t>EMSN071</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B531" t="inlineStr">
         <is>
           <t>[{'short_name': 'Germany'}]</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C531" t="inlineStr">
         <is>
           <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr">
+      <c r="D531" t="inlineStr">
         <is>
           <t>Wildfires, Preparedness, Arnsberg, Germany</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr">
+      <c r="E531" t="inlineStr">
         <is>
           <t>POINT (8.021859999999998 51.41891999999999)</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr">
+      <c r="F531" t="inlineStr">
         <is>
           <t>2020-04-09T01:00:00</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr">
+      <c r="G531" t="inlineStr">
         <is>
           <t>2026-01-20T09:58:16.184451</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
+      <c r="H531" t="inlineStr">
         <is>
           <t>preparedness</t>
         </is>
       </c>
-      <c r="I530" t="b">
-        <v>1</v>
-      </c>
-      <c r="J530" t="n">
-        <v>1</v>
-      </c>
-      <c r="K530" t="n">
+      <c r="I531" t="b">
+        <v>1</v>
+      </c>
+      <c r="J531" t="n">
+        <v>1</v>
+      </c>
+      <c r="K531" t="n">
         <v>4</v>
       </c>
-      <c r="L530" t="inlineStr">
+      <c r="L531" t="inlineStr">
         <is>
           <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could...</t>
         </is>
       </c>
-      <c r="M530" t="inlineStr">
+      <c r="M531" t="inlineStr">
         <is>
           <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could hit this territory.
 More than 63% of the town’s area is covered by forest, including several large protected areas; forest plays an important economic role in both tourism and the timber-processing busi Reference map (Overview A1) Land Use Land Cover map (Overview A1) Pre-disaster forest fire hazard (Overview A1) Pre-disaster forest fire exposure (Overview A1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>EMSN066</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Iran'}]</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>Flood delineation and flood damage assessment, Iran</t>
-        </is>
-      </c>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>POINT (58.96228 25.99307)</t>
-        </is>
-      </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>2020-04-09T01:00:00</t>
-        </is>
-      </c>
-      <c r="G531" t="inlineStr"/>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I531" t="b">
-        <v>1</v>
-      </c>
-      <c r="J531" t="n">
-        <v>3</v>
-      </c>
-      <c r="K531" t="n">
-        <v>11</v>
-      </c>
-      <c r="L531" t="inlineStr"/>
-      <c r="M531" t="inlineStr">
-        <is>
-          <t>The scope of the service request EMSN-066 is to delineate the extent and assess damage of 9 to 11 January 2020 flood event, in South-East Iran. As predicted by Copernicus EMS service GloFAS, days of heavy rain from 9 to 11 January 2020 caused severe flooding in southern Iran, in Sistan and Baluchestan, Hormozgan and south of Kerman provinces. Flooding has blocked roads and damaged houses, bridges, crops and infrastructure. Dozens of areas have been left isolated after roads were damaged or block Reservoir and dam change detection (Overview A3) Reference map (Overview A3) Flood delineation (Overview A3) Damage assessment (Overview A3) Reference map (Overview A2) Flood delineation (Overview A2) Damage assessment (Overview A2) Reservoir and dam change detection (Overview A1) Reference map (Overview A1) Flood delineation (Overview A1)</t>
         </is>
       </c>
     </row>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-02-16T13:13:53.983017</t>
+          <t>2026-03-10T14:33:18.287330</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -645,7 +645,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EMSR821</t>
+          <t>EMSR820</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wildfire in Peloponnese, Greece</t>
+          <t>Wildfire in East Attica, Greece</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>POINT (21.790352 37.231148)</t>
+          <t>POINT (23.802395 38.169519)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2025-07-28T15:11:33.550671</t>
+          <t>2025-07-28T13:24:34.744611</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2632,11 +2632,11 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>On the 26 July 2025 at 15:08 (CET), a wildfire was reported to have affected the area very close to Aetos in Peloponnese Region, Greece. The fire expanded rapidly; residents of Aetos and Monastiri had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces an...</t>
+          <t>On the 26 July 2025 at 18:24 (CET), a wildfire was reported to have affected the area near Krioneri, in the outskirts of Athens, Greece. The fire expanded rapidly; residents of Krioneri and Drosopigi had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces...</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EMSR820</t>
+          <t>EMSR821</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wildfire in East Attica, Greece</t>
+          <t>Wildfire in Peloponnese, Greece</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>POINT (23.802395 38.169519)</t>
+          <t>POINT (21.790352 37.231148)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-07-28T13:24:34.744611</t>
+          <t>2025-07-28T15:11:33.550671</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2689,11 +2689,11 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>On the 26 July 2025 at 18:24 (CET), a wildfire was reported to have affected the area near Krioneri, in the outskirts of Athens, Greece. The fire expanded rapidly; residents of Krioneri and Drosopigi had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces...</t>
+          <t>On the 26 July 2025 at 15:08 (CET), a wildfire was reported to have affected the area very close to Aetos in Peloponnese Region, Greece. The fire expanded rapidly; residents of Aetos and Monastiri had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces an...</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-03T15:30:15.413063</t>
+          <t>2026-03-16T13:02:17.930667</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-02-06T12:24:31.454239</t>
+          <t>2026-04-08T07:13:02.738522</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2587,7 +2587,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EMSR820</t>
+          <t>EMSR821</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wildfire in East Attica, Greece</t>
+          <t>Wildfire in Peloponnese, Greece</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>POINT (23.802395 38.169519)</t>
+          <t>POINT (21.790352 37.231148)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2025-07-28T13:24:34.744611</t>
+          <t>2025-07-28T15:11:33.550671</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2632,11 +2632,11 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>On the 26 July 2025 at 18:24 (CET), a wildfire was reported to have affected the area near Krioneri, in the outskirts of Athens, Greece. The fire expanded rapidly; residents of Krioneri and Drosopigi had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces...</t>
+          <t>On the 26 July 2025 at 15:08 (CET), a wildfire was reported to have affected the area very close to Aetos in Peloponnese Region, Greece. The fire expanded rapidly; residents of Aetos and Monastiri had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces an...</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EMSR821</t>
+          <t>EMSR820</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wildfire in Peloponnese, Greece</t>
+          <t>Wildfire in East Attica, Greece</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>POINT (21.790352 37.231148)</t>
+          <t>POINT (23.802395 38.169519)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-07-28T15:11:33.550671</t>
+          <t>2025-07-28T13:24:34.744611</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2689,11 +2689,11 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>On the 26 July 2025 at 15:08 (CET), a wildfire was reported to have affected the area very close to Aetos in Peloponnese Region, Greece. The fire expanded rapidly; residents of Aetos and Monastiri had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces an...</t>
+          <t>On the 26 July 2025 at 18:24 (CET), a wildfire was reported to have affected the area near Krioneri, in the outskirts of Athens, Greece. The fire expanded rapidly; residents of Krioneri and Drosopigi had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces...</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-10T14:33:18.287330</t>
+          <t>2026-04-14T14:01:14.376717</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -645,7 +645,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-16T13:02:17.930667</t>
+          <t>2026-04-21T09:46:00.165543</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-08T07:13:02.738522</t>
+          <t>2026-04-21T14:55:39.171141</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="I7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -2587,7 +2587,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EMSR821</t>
+          <t>EMSR820</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wildfire in Peloponnese, Greece</t>
+          <t>Wildfire in East Attica, Greece</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>POINT (21.790352 37.231148)</t>
+          <t>POINT (23.802395 38.169519)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2025-07-28T15:11:33.550671</t>
+          <t>2025-07-28T13:24:34.744611</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2632,11 +2632,11 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>On the 26 July 2025 at 15:08 (CET), a wildfire was reported to have affected the area very close to Aetos in Peloponnese Region, Greece. The fire expanded rapidly; residents of Aetos and Monastiri had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces an...</t>
+          <t>On the 26 July 2025 at 18:24 (CET), a wildfire was reported to have affected the area near Krioneri, in the outskirts of Athens, Greece. The fire expanded rapidly; residents of Krioneri and Drosopigi had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces...</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EMSR820</t>
+          <t>EMSR821</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wildfire in East Attica, Greece</t>
+          <t>Wildfire in Peloponnese, Greece</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>POINT (23.802395 38.169519)</t>
+          <t>POINT (21.790352 37.231148)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-07-28T13:24:34.744611</t>
+          <t>2025-07-28T15:11:33.550671</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2689,11 +2689,11 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>On the 26 July 2025 at 18:24 (CET), a wildfire was reported to have affected the area near Krioneri, in the outskirts of Athens, Greece. The fire expanded rapidly; residents of Krioneri and Drosopigi had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces...</t>
+          <t>On the 26 July 2025 at 15:08 (CET), a wildfire was reported to have affected the area very close to Aetos in Peloponnese Region, Greece. The fire expanded rapidly; residents of Aetos and Monastiri had to be evacuated, and a 112 cell-broadcasting message was sent for this purpose. Ground forces an...</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-14T14:01:14.376717</t>
+          <t>2026-05-15T07:31:47.075243</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="I6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -21873,7 +21873,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>EMSN110</t>
+          <t>EMSN108</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -21888,12 +21888,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Wildfire in Alburquerque, Spain</t>
+          <t>Wildfire in San Felices de los Gallegos, Spain</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>POINT (-6.85472 40.02093)</t>
+          <t>POINT (-6.67526 40.8026)</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -21918,19 +21918,19 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>EMSN108</t>
+          <t>EMSN110</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -21945,12 +21945,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Wildfire in San Felices de los Gallegos, Spain</t>
+          <t>Wildfire in Alburquerque, Spain</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>POINT (-6.67526 40.8026)</t>
+          <t>POINT (-6.85472 40.02093)</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -21975,12 +21975,12 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -23532,7 +23532,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EMSN101</t>
+          <t>EMSN100</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -23547,12 +23547,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Wildfire in Ciudad Real, Spain</t>
+          <t>Wildfires in La Rioja, Spain</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>POINT (-4.85493 38.75007)</t>
+          <t>POINT (-2.01861 42.15347)</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -23577,19 +23577,19 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>EMSN100</t>
+          <t>EMSN101</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -23604,12 +23604,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Wildfires in La Rioja, Spain</t>
+          <t>Wildfire in Ciudad Real, Spain</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>POINT (-2.01861 42.15347)</t>
+          <t>POINT (-4.85493 38.75007)</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -23634,12 +23634,12 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -30710,27 +30710,27 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>EMSN063</t>
+          <t>EMSN064</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Nigeria'}]</t>
+          <t>[{'short_name': 'Ukraine'}]</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Crop change detection in conflict areas, Nigeria</t>
+          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>POINT (12.36791 13.49555)</t>
+          <t>POINT (23.87015 47.95273)</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -30748,74 +30748,74 @@
         <v>1</v>
       </c>
       <c r="J544" t="n">
+        <v>1</v>
+      </c>
+      <c r="K544" t="n">
+        <v>4</v>
+      </c>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>The scope is the assessment of the sinkhole risk in the mining area of Solotvyno, Zakarpattya region, Ukraine, in continuation of the previous serviceEMSN-030. A systematic salt mining began in the second half of the 18th century with up to eight salt mines in operation. Although the flooding with ground water and the erosion of subsoil salt layers began in the early 2000s, the extraction of salt had not been completely stopped until 2010, when in December 3000m³ of land collapsed.
+The aim is t Surface Dynamics Map Subsidence and Landslide Risk Map Reference map Land use/ land cover map</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>EMSN063</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Nigeria'}]</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Crop change detection in conflict areas, Nigeria</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>POINT (12.36791 13.49555)</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2020-02-14T01:00:00</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I545" t="b">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
         <v>5</v>
       </c>
-      <c r="K544" t="n">
+      <c r="K545" t="n">
         <v>5</v>
       </c>
-      <c r="L544" t="inlineStr">
+      <c r="L545" t="inlineStr">
         <is>
           <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been ac...</t>
         </is>
       </c>
-      <c r="M544" t="inlineStr">
+      <c r="M545" t="inlineStr">
         <is>
           <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been accessed for several years and little to no data could be collected due to intense fighting activities by Boko Haram since 2010.
 The aim of the activation is a crop change analysis implemented between the Crop Change Crop Change Crop Change Crop Change Crop Change</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>EMSN064</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Ukraine'}]</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>POINT (23.87015 47.95273)</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>2020-02-14T01:00:00</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr"/>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I545" t="b">
-        <v>1</v>
-      </c>
-      <c r="J545" t="n">
-        <v>1</v>
-      </c>
-      <c r="K545" t="n">
-        <v>4</v>
-      </c>
-      <c r="L545" t="inlineStr"/>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>The scope is the assessment of the sinkhole risk in the mining area of Solotvyno, Zakarpattya region, Ukraine, in continuation of the previous serviceEMSN-030. A systematic salt mining began in the second half of the 18th century with up to eight salt mines in operation. Although the flooding with ground water and the erosion of subsoil salt layers began in the early 2000s, the extraction of salt had not been completely stopped until 2010, when in December 3000m³ of land collapsed.
-The aim is t Surface Dynamics Map Subsidence and Landslide Risk Map Reference map Land use/ land cover map</t>
         </is>
       </c>
     </row>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -21873,7 +21873,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>EMSN108</t>
+          <t>EMSN110</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -21888,12 +21888,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Wildfire in San Felices de los Gallegos, Spain</t>
+          <t>Wildfire in Alburquerque, Spain</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>POINT (-6.67526 40.8026)</t>
+          <t>POINT (-6.85472 40.02093)</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -21918,19 +21918,19 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>EMSN110</t>
+          <t>EMSN108</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -21945,12 +21945,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Wildfire in Alburquerque, Spain</t>
+          <t>Wildfire in San Felices de los Gallegos, Spain</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>POINT (-6.85472 40.02093)</t>
+          <t>POINT (-6.67526 40.8026)</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -21975,12 +21975,12 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -23532,7 +23532,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EMSN100</t>
+          <t>EMSN101</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -23547,12 +23547,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Wildfires in La Rioja, Spain</t>
+          <t>Wildfire in Ciudad Real, Spain</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>POINT (-2.01861 42.15347)</t>
+          <t>POINT (-4.85493 38.75007)</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -23577,19 +23577,19 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>EMSN101</t>
+          <t>EMSN100</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -23604,12 +23604,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Wildfire in Ciudad Real, Spain</t>
+          <t>Wildfires in La Rioja, Spain</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>POINT (-4.85493 38.75007)</t>
+          <t>POINT (-2.01861 42.15347)</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -23634,12 +23634,12 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -30710,27 +30710,27 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>EMSN064</t>
+          <t>EMSN063</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Ukraine'}]</t>
+          <t>[{'short_name': 'Nigeria'}]</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
+          <t>Crop change detection in conflict areas, Nigeria</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>POINT (23.87015 47.95273)</t>
+          <t>POINT (12.36791 13.49555)</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -30748,74 +30748,74 @@
         <v>1</v>
       </c>
       <c r="J544" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K544" t="n">
+        <v>5</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been ac...</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been accessed for several years and little to no data could be collected due to intense fighting activities by Boko Haram since 2010.
+The aim of the activation is a crop change analysis implemented between the Crop Change Crop Change Crop Change Crop Change Crop Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>EMSN064</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Ukraine'}]</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>POINT (23.87015 47.95273)</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2020-02-14T01:00:00</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I545" t="b">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
+        <v>1</v>
+      </c>
+      <c r="K545" t="n">
         <v>4</v>
       </c>
-      <c r="L544" t="inlineStr"/>
-      <c r="M544" t="inlineStr">
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr">
         <is>
           <t>The scope is the assessment of the sinkhole risk in the mining area of Solotvyno, Zakarpattya region, Ukraine, in continuation of the previous serviceEMSN-030. A systematic salt mining began in the second half of the 18th century with up to eight salt mines in operation. Although the flooding with ground water and the erosion of subsoil salt layers began in the early 2000s, the extraction of salt had not been completely stopped until 2010, when in December 3000m³ of land collapsed.
 The aim is t Surface Dynamics Map Subsidence and Landslide Risk Map Reference map Land use/ land cover map</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>EMSN063</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Nigeria'}]</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>Crop change detection in conflict areas, Nigeria</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>POINT (12.36791 13.49555)</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>2020-02-14T01:00:00</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr"/>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I545" t="b">
-        <v>1</v>
-      </c>
-      <c r="J545" t="n">
-        <v>5</v>
-      </c>
-      <c r="K545" t="n">
-        <v>5</v>
-      </c>
-      <c r="L545" t="inlineStr">
-        <is>
-          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been ac...</t>
-        </is>
-      </c>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been accessed for several years and little to no data could be collected due to intense fighting activities by Boko Haram since 2010.
-The aim of the activation is a crop change analysis implemented between the Crop Change Crop Change Crop Change Crop Change Crop Change</t>
         </is>
       </c>
     </row>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-15T07:31:47.075243</t>
+          <t>2026-06-08T14:11:17.650485</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21873,7 +21873,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>EMSN110</t>
+          <t>EMSN108</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -21888,12 +21888,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Wildfire in Alburquerque, Spain</t>
+          <t>Wildfire in San Felices de los Gallegos, Spain</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>POINT (-6.85472 40.02093)</t>
+          <t>POINT (-6.67526 40.8026)</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -21918,19 +21918,19 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>EMSN108</t>
+          <t>EMSN110</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -21945,12 +21945,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Wildfire in San Felices de los Gallegos, Spain</t>
+          <t>Wildfire in Alburquerque, Spain</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>POINT (-6.67526 40.8026)</t>
+          <t>POINT (-6.85472 40.02093)</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -21975,12 +21975,12 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -23532,7 +23532,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EMSN101</t>
+          <t>EMSN100</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -23547,12 +23547,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Wildfire in Ciudad Real, Spain</t>
+          <t>Wildfires in La Rioja, Spain</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>POINT (-4.85493 38.75007)</t>
+          <t>POINT (-2.01861 42.15347)</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -23577,19 +23577,19 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>EMSN100</t>
+          <t>EMSN101</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -23604,12 +23604,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Wildfires in La Rioja, Spain</t>
+          <t>Wildfire in Ciudad Real, Spain</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>POINT (-2.01861 42.15347)</t>
+          <t>POINT (-4.85493 38.75007)</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -23634,12 +23634,12 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -30710,27 +30710,27 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>EMSN063</t>
+          <t>EMSN064</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Nigeria'}]</t>
+          <t>[{'short_name': 'Ukraine'}]</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Crop change detection in conflict areas, Nigeria</t>
+          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>POINT (12.36791 13.49555)</t>
+          <t>POINT (23.87015 47.95273)</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -30748,74 +30748,74 @@
         <v>1</v>
       </c>
       <c r="J544" t="n">
+        <v>1</v>
+      </c>
+      <c r="K544" t="n">
+        <v>4</v>
+      </c>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>The scope is the assessment of the sinkhole risk in the mining area of Solotvyno, Zakarpattya region, Ukraine, in continuation of the previous serviceEMSN-030. A systematic salt mining began in the second half of the 18th century with up to eight salt mines in operation. Although the flooding with ground water and the erosion of subsoil salt layers began in the early 2000s, the extraction of salt had not been completely stopped until 2010, when in December 3000m³ of land collapsed.
+The aim is t Surface Dynamics Map Subsidence and Landslide Risk Map Reference map Land use/ land cover map</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>EMSN063</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Nigeria'}]</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Crop change detection in conflict areas, Nigeria</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>POINT (12.36791 13.49555)</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2020-02-14T01:00:00</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I545" t="b">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
         <v>5</v>
       </c>
-      <c r="K544" t="n">
+      <c r="K545" t="n">
         <v>5</v>
       </c>
-      <c r="L544" t="inlineStr">
+      <c r="L545" t="inlineStr">
         <is>
           <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been ac...</t>
         </is>
       </c>
-      <c r="M544" t="inlineStr">
+      <c r="M545" t="inlineStr">
         <is>
           <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been accessed for several years and little to no data could be collected due to intense fighting activities by Boko Haram since 2010.
 The aim of the activation is a crop change analysis implemented between the Crop Change Crop Change Crop Change Crop Change Crop Change</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>EMSN064</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Ukraine'}]</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>POINT (23.87015 47.95273)</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>2020-02-14T01:00:00</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr"/>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I545" t="b">
-        <v>1</v>
-      </c>
-      <c r="J545" t="n">
-        <v>1</v>
-      </c>
-      <c r="K545" t="n">
-        <v>4</v>
-      </c>
-      <c r="L545" t="inlineStr"/>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>The scope is the assessment of the sinkhole risk in the mining area of Solotvyno, Zakarpattya region, Ukraine, in continuation of the previous serviceEMSN-030. A systematic salt mining began in the second half of the 18th century with up to eight salt mines in operation. Although the flooding with ground water and the erosion of subsoil salt layers began in the early 2000s, the extraction of salt had not been completely stopped until 2010, when in December 3000m³ of land collapsed.
-The aim is t Surface Dynamics Map Subsidence and Landslide Risk Map Reference map Land use/ land cover map</t>
         </is>
       </c>
     </row>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-08T14:11:17.650485</t>
+          <t>2026-06-18T13:05:50.852732</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -10258,27 +10258,27 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EMSN183</t>
+          <t>EMSN184</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Spain'}]</t>
+          <t>[{'short_name': 'Greece'}]</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Forest fire impact assessment in Sierra de Los Guajares, Spain</t>
+          <t>Flood in Thessaly Region, Greece</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>POINT (3.60201 36.85033)</t>
+          <t>POINT (23.19128 38.87509)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10299,7 +10299,7 @@
         <v>1</v>
       </c>
       <c r="K178" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
@@ -10307,27 +10307,27 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>EMSN184</t>
+          <t>EMSN183</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Greece'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Flood in Thessaly Region, Greece</t>
+          <t>Forest fire impact assessment in Sierra de Los Guajares, Spain</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>POINT (23.19128 38.87509)</t>
+          <t>POINT (3.60201 36.85033)</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -10348,7 +10348,7 @@
         <v>1</v>
       </c>
       <c r="K179" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
@@ -11955,7 +11955,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EMSR689</t>
+          <t>EMSR688</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Wildfire in Rodopi, Greece</t>
+          <t>Wildfire in Euboea Island, Greece</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>POINT (25.504761 41.090738)</t>
+          <t>POINT (23.732529 38.452917)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2023-11-28T09:27:40.534169</t>
+          <t>2023-11-28T09:47:05.454890</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -11997,10 +11997,10 @@
         <v>1</v>
       </c>
       <c r="J209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K209" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
@@ -12008,7 +12008,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>EMSR688</t>
+          <t>EMSR689</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12023,12 +12023,12 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Wildfire in Euboea Island, Greece</t>
+          <t>Wildfire in Rodopi, Greece</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>POINT (23.732529 38.452917)</t>
+          <t>POINT (25.504761 41.090738)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2023-11-28T09:47:05.454890</t>
+          <t>2023-11-28T09:27:40.534169</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -12050,10 +12050,10 @@
         <v>1</v>
       </c>
       <c r="J210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K210" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
@@ -21816,7 +21816,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>EMSN109</t>
+          <t>EMSN110</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -21831,12 +21831,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Wildfire in Alcaracejos, Spain</t>
+          <t>Wildfire in Alburquerque, Spain</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>POINT (-4.94932 38.2282)</t>
+          <t>POINT (-6.85472 40.02093)</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -21866,14 +21866,14 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>EMSN108</t>
+          <t>EMSN109</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -21888,12 +21888,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Wildfire in San Felices de los Gallegos, Spain</t>
+          <t>Wildfire in Alcaracejos, Spain</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>POINT (-6.67526 40.8026)</t>
+          <t>POINT (-4.94932 38.2282)</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -21918,19 +21918,19 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>EMSN110</t>
+          <t>EMSN108</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -21945,12 +21945,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Wildfire in Alburquerque, Spain</t>
+          <t>Wildfire in San Felices de los Gallegos, Spain</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>POINT (-6.85472 40.02093)</t>
+          <t>POINT (-6.67526 40.8026)</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -21975,12 +21975,12 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -23304,27 +23304,27 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>EMSN103</t>
+          <t>EMSN102</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Central African Republic'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>IDP camp monitoring in Bria, Central African Republic</t>
+          <t>Wildfires in Huelva, Spain</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>POINT (21.9657 6.54857)</t>
+          <t>POINT (-6.61875 37.43943)</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -23345,43 +23345,43 @@
         <v>1</v>
       </c>
       <c r="K415" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d P19-Population displacement location P19-MONIT01-Overview Map P19-Overview Map P19-Population displacement location-MONIT01</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>EMSN102</t>
+          <t>EMSN103</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Spain'}]</t>
+          <t>[{'short_name': 'Central African Republic'}]</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Wildfires in Huelva, Spain</t>
+          <t>IDP camp monitoring in Bria, Central African Republic</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>POINT (-6.61875 37.43943)</t>
+          <t>POINT (21.9657 6.54857)</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -23402,16 +23402,16 @@
         <v>1</v>
       </c>
       <c r="K416" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d P19-Population displacement location P19-MONIT01-Overview Map P19-Overview Map P19-Population displacement location-MONIT01</t>
         </is>
       </c>
     </row>
@@ -30710,27 +30710,27 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>EMSN064</t>
+          <t>EMSN063</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Ukraine'}]</t>
+          <t>[{'short_name': 'Nigeria'}]</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
+          <t>Crop change detection in conflict areas, Nigeria</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>POINT (23.87015 47.95273)</t>
+          <t>POINT (12.36791 13.49555)</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -30748,74 +30748,74 @@
         <v>1</v>
       </c>
       <c r="J544" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K544" t="n">
+        <v>5</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been ac...</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been accessed for several years and little to no data could be collected due to intense fighting activities by Boko Haram since 2010.
+The aim of the activation is a crop change analysis implemented between the Crop Change Crop Change Crop Change Crop Change Crop Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>EMSN064</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Ukraine'}]</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>POINT (23.87015 47.95273)</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2020-02-14T01:00:00</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I545" t="b">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
+        <v>1</v>
+      </c>
+      <c r="K545" t="n">
         <v>4</v>
       </c>
-      <c r="L544" t="inlineStr"/>
-      <c r="M544" t="inlineStr">
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr">
         <is>
           <t>The scope is the assessment of the sinkhole risk in the mining area of Solotvyno, Zakarpattya region, Ukraine, in continuation of the previous serviceEMSN-030. A systematic salt mining began in the second half of the 18th century with up to eight salt mines in operation. Although the flooding with ground water and the erosion of subsoil salt layers began in the early 2000s, the extraction of salt had not been completely stopped until 2010, when in December 3000m³ of land collapsed.
 The aim is t Surface Dynamics Map Subsidence and Landslide Risk Map Reference map Land use/ land cover map</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>EMSN063</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Nigeria'}]</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>Crop change detection in conflict areas, Nigeria</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>POINT (12.36791 13.49555)</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>2020-02-14T01:00:00</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr"/>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I545" t="b">
-        <v>1</v>
-      </c>
-      <c r="J545" t="n">
-        <v>5</v>
-      </c>
-      <c r="K545" t="n">
-        <v>5</v>
-      </c>
-      <c r="L545" t="inlineStr">
-        <is>
-          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been ac...</t>
-        </is>
-      </c>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been accessed for several years and little to no data could be collected due to intense fighting activities by Boko Haram since 2010.
-The aim of the activation is a crop change analysis implemented between the Crop Change Crop Change Crop Change Crop Change Crop Change</t>
         </is>
       </c>
     </row>
@@ -44440,60 +44440,115 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
+          <t>EMSN033</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Libya'}]</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Satellite based conflict damage assessment of two selected cities in Libya</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>POINT (21.79769 28.28583)</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>2017-03-08T01:00:00</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr"/>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I785" t="b">
+        <v>1</v>
+      </c>
+      <c r="J785" t="n">
+        <v>3</v>
+      </c>
+      <c r="K785" t="n">
+        <v>68</v>
+      </c>
+      <c r="L785" t="inlineStr"/>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>EMSN033 is a satellite based conflict damage assessment of three selected areas of interest (AOIs) in Libya: Benghazi city, Benghazi´s Aerodrome (El Benina) and Al-Jawf.
+The scope of the map production was to generate general reference content of the pre-event situation, including administrative boundaries, road network, urban land use classification, urban sprawl and urban expansion velocity analysis.
+The core users of the map are the Foreign Policy Instruments (FPI) of the European Commi Urban velocity map (Overview A1) Urban velocity map (Overview A1) Urban Sprawl map (Overview A1) Urban Sprawl map (Overview A1) Urban Sprawl map (Overview A1) Reference map (Overview A1) Reference map (Overview A1) Reference map (Overview A1) Reference map (Detail B2) Reference map (Detail B2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
           <t>EMSN038</t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>[{'short_name': 'Peru'}]</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
-      <c r="D785" t="inlineStr">
+      <c r="D786" t="inlineStr">
         <is>
           <t>Post-disaster situation analyses of flood and landslides in Lima, Peru</t>
         </is>
       </c>
-      <c r="E785" t="inlineStr">
+      <c r="E786" t="inlineStr">
         <is>
           <t>POINT (-76.95929999999998 -11.886920000000007)</t>
         </is>
       </c>
-      <c r="F785" t="inlineStr">
+      <c r="F786" t="inlineStr">
         <is>
           <t>2017-03-08T01:00:00</t>
         </is>
       </c>
-      <c r="G785" t="inlineStr">
+      <c r="G786" t="inlineStr">
         <is>
           <t>2026-01-20T09:57:00.365888</t>
         </is>
       </c>
-      <c r="H785" t="inlineStr">
+      <c r="H786" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="I785" t="b">
-        <v>1</v>
-      </c>
-      <c r="J785" t="n">
-        <v>1</v>
-      </c>
-      <c r="K785" t="n">
+      <c r="I786" t="b">
+        <v>1</v>
+      </c>
+      <c r="J786" t="n">
+        <v>1</v>
+      </c>
+      <c r="K786" t="n">
         <v>5</v>
       </c>
-      <c r="L785" t="inlineStr">
+      <c r="L786" t="inlineStr">
         <is>
           <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
 The scope of the map production is t...</t>
         </is>
       </c>
-      <c r="M785" t="inlineStr">
+      <c r="M786" t="inlineStr">
         <is>
           <t>Post-disaster situation analyses of the flood that occurred in mid-March 2017 in Lima, Peru. Heavy rains affected nearly all of Peru leading to catastrophic flooding and landslides. In northern Lima, flooded areas along Rímac and Chillón rivers were reported.
 The scope of the map production is to generate a pre-event reference content, delineate the event impact and grade the damage, focusing on people and assets, with particular attention to schools in the metropolitan area  of northern Lima.
@@ -44501,61 +44556,6 @@
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
-        <is>
-          <t>EMSN033</t>
-        </is>
-      </c>
-      <c r="B786" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Libya'}]</t>
-        </is>
-      </c>
-      <c r="C786" t="inlineStr">
-        <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
-        </is>
-      </c>
-      <c r="D786" t="inlineStr">
-        <is>
-          <t>Satellite based conflict damage assessment of two selected cities in Libya</t>
-        </is>
-      </c>
-      <c r="E786" t="inlineStr">
-        <is>
-          <t>POINT (21.79769 28.28583)</t>
-        </is>
-      </c>
-      <c r="F786" t="inlineStr">
-        <is>
-          <t>2017-03-08T01:00:00</t>
-        </is>
-      </c>
-      <c r="G786" t="inlineStr"/>
-      <c r="H786" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I786" t="b">
-        <v>1</v>
-      </c>
-      <c r="J786" t="n">
-        <v>3</v>
-      </c>
-      <c r="K786" t="n">
-        <v>68</v>
-      </c>
-      <c r="L786" t="inlineStr"/>
-      <c r="M786" t="inlineStr">
-        <is>
-          <t>EMSN033 is a satellite based conflict damage assessment of three selected areas of interest (AOIs) in Libya: Benghazi city, Benghazi´s Aerodrome (El Benina) and Al-Jawf.
-The scope of the map production was to generate general reference content of the pre-event situation, including administrative boundaries, road network, urban land use classification, urban sprawl and urban expansion velocity analysis.
-The core users of the map are the Foreign Policy Instruments (FPI) of the European Commi Urban velocity map (Overview A1) Urban velocity map (Overview A1) Urban Sprawl map (Overview A1) Urban Sprawl map (Overview A1) Urban Sprawl map (Overview A1) Reference map (Overview A1) Reference map (Overview A1) Reference map (Overview A1) Reference map (Detail B2) Reference map (Detail B2)</t>
-        </is>
-      </c>
-    </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
@@ -44907,117 +44907,117 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
+          <t>EMSN030</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Ukraine'}]</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Ground deformation mapping and monitoring by satellite based multi-temporal DInSAR technique</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>POINT (23.86 47.95)</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>2016-10-17T01:00:00</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr"/>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I793" t="b">
+        <v>1</v>
+      </c>
+      <c r="J793" t="n">
+        <v>1</v>
+      </c>
+      <c r="K793" t="n">
+        <v>40</v>
+      </c>
+      <c r="L793" t="inlineStr"/>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>EMSN030 was activated by the National Directorate General for Disaster Management, Hungary, on behalf of the EUCPT (Scoping Mission in Solotvyno salt mine, Ukraine) on 12/7/2016. The crisis related to the structural deterioration of old salt mines due to flooding of mine shafts and subsequent contamination of the Tisza River. Underground cavities and sinkholes emerged, threatening the local population, as well as industrial buildings and engineering systems.
+In order to monitor the ground def Current Trends Map - Sinkhole and Landslides Risk Map Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1004) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1003) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1002) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1001) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1004) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1003) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1002) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
           <t>EMSN032</t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>[{'short_name': 'Portugal'}]</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
-      <c r="D793" t="inlineStr">
+      <c r="D794" t="inlineStr">
         <is>
           <t>Forest fire damage assessment, Portugal</t>
         </is>
       </c>
-      <c r="E793" t="inlineStr">
+      <c r="E794" t="inlineStr">
         <is>
           <t>POINT (-8.21612 40.898399999999995)</t>
         </is>
       </c>
-      <c r="F793" t="inlineStr">
+      <c r="F794" t="inlineStr">
         <is>
           <t>2016-10-17T01:00:00</t>
         </is>
       </c>
-      <c r="G793" t="inlineStr">
+      <c r="G794" t="inlineStr">
         <is>
           <t>2026-01-20T09:56:25.083357</t>
         </is>
       </c>
-      <c r="H793" t="inlineStr">
+      <c r="H794" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="I793" t="b">
-        <v>1</v>
-      </c>
-      <c r="J793" t="n">
-        <v>1</v>
-      </c>
-      <c r="K793" t="n">
+      <c r="I794" t="b">
+        <v>1</v>
+      </c>
+      <c r="J794" t="n">
+        <v>1</v>
+      </c>
+      <c r="K794" t="n">
         <v>120</v>
       </c>
-      <c r="L793" t="inlineStr">
+      <c r="L794" t="inlineStr">
         <is>
           <t>The scope of the service request EMSN032 is to generate damage delineation and grading maps of 41 different forest fires in mainland Portugal that occurred in July and August 2016. The affected area had an overall extent of 887 km².
 The service consists of detailed reference maps and damage de...</t>
         </is>
       </c>
-      <c r="M793" t="inlineStr">
+      <c r="M794" t="inlineStr">
         <is>
           <t>The scope of the service request EMSN032 is to generate damage delineation and grading maps of 41 different forest fires in mainland Portugal that occurred in July and August 2016. The affected area had an overall extent of 887 km².
 The service consists of detailed reference maps and damage delineation and grading. Additionally, assessment of post-event slope stability, erosion and accessibility to the affected areas were requested. All layers were produced at the cartographic scale of 1:25,0 Reference map Assessment of Access Erosion Risk Fire Delineation and Grading Landslide Risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
-        <is>
-          <t>EMSN030</t>
-        </is>
-      </c>
-      <c r="B794" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Ukraine'}]</t>
-        </is>
-      </c>
-      <c r="C794" t="inlineStr">
-        <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
-        </is>
-      </c>
-      <c r="D794" t="inlineStr">
-        <is>
-          <t>Ground deformation mapping and monitoring by satellite based multi-temporal DInSAR technique</t>
-        </is>
-      </c>
-      <c r="E794" t="inlineStr">
-        <is>
-          <t>POINT (23.86 47.95)</t>
-        </is>
-      </c>
-      <c r="F794" t="inlineStr">
-        <is>
-          <t>2016-10-17T01:00:00</t>
-        </is>
-      </c>
-      <c r="G794" t="inlineStr"/>
-      <c r="H794" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I794" t="b">
-        <v>1</v>
-      </c>
-      <c r="J794" t="n">
-        <v>1</v>
-      </c>
-      <c r="K794" t="n">
-        <v>40</v>
-      </c>
-      <c r="L794" t="inlineStr"/>
-      <c r="M794" t="inlineStr">
-        <is>
-          <t>EMSN030 was activated by the National Directorate General for Disaster Management, Hungary, on behalf of the EUCPT (Scoping Mission in Solotvyno salt mine, Ukraine) on 12/7/2016. The crisis related to the structural deterioration of old salt mines due to flooding of mine shafts and subsequent contamination of the Tisza River. Underground cavities and sinkholes emerged, threatening the local population, as well as industrial buildings and engineering systems.
-In order to monitor the ground def Current Trends Map - Sinkhole and Landslides Risk Map Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1004) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1003) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1002) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1001) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1004) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1003) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1002) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1001)</t>
         </is>
       </c>
     </row>
@@ -46209,12 +46209,12 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>EMSN025</t>
+          <t>EMSN029</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Greece'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -46224,12 +46224,12 @@
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Forest fire damage assessment – Planning and Recovery</t>
+          <t>Forest fire damage assessment - new risks and mitigation</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>POINT (25.579999999999995 38.34999999999999)</t>
+          <t>POINT (-0.54267 40.01794999999999)</t>
         </is>
       </c>
       <c r="F816" t="inlineStr">
@@ -46239,7 +46239,7 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>2026-01-20T09:54:14.348681</t>
+          <t>2026-01-20T09:55:03.938401</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
@@ -46251,79 +46251,17 @@
         <v>1</v>
       </c>
       <c r="J816" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K816" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="L816" t="inlineStr">
         <is>
-          <t>This activation focuses on damage delineation and grading maps for selected forest fires in Greece in the summer of 2015. Additionally, loss assessment and risk assessment products (landslide/erosion and flash flood) including, mitigation and recovery measures are analysed. Key assets (infrastruc...</t>
+          <t>Two areas of Special Areas of Conservation: Sierra de Espadn and Curs Alt del riu Millars were hit by a forest fire in July 2015, in the Montn and Caudiel municipalities of the region of Valencia. The analysis of the damage degree and landslide and erosion risk is of key importance for the spatia...</t>
         </is>
       </c>
       <c r="M816" t="inlineStr">
-        <is>
-          <t>This activation focuses on damage delineation and grading maps for selected forest fires in Greece in the summer of 2015. Additionally, loss assessment and risk assessment products (landslide/erosion and flash flood) including, mitigation and recovery measures are analysed. Key assets (infrastructure, environment, human life, economic sustainability, etc.) are also identified and related with the probability and severity (impact) of potential (secondary) hazards.
-The activation was triggered  Assets and Trans. Networks at Risk Map - Flood Risk Assessment (Details, Tile 6011) Soil Loss Map - Erosion Hazard Zones (Details, Tile 6011) Assets and Trans. Networks at Risk Map - Landslide Risk Assessment (Details, Tile 6011) Land Use and Land Cover Map - Multiple Natural Hazard Risk Assessment (Details, Tile 6011) Biomass Loss Assessment Map - Fire Damage Assessment (Details, Tile 6011) Delineation and Grading Map - Fire Damage Assessment (Details, Tile 6011) Reference Map - Multiple Natural Hazard Risk Assessment (Details, Tile 6011) Assets and Trans. Networks at Risk Map - Flood Risk Assessment (Details, Tile 5010) Soil Loss Map - Erosion Hazard Zones (Details, Tile 5010) Assets and Trans. Networks at Risk Map - Landslide Risk Assessment (Details, Tile 5010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>EMSN029</t>
-        </is>
-      </c>
-      <c r="B817" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Spain'}]</t>
-        </is>
-      </c>
-      <c r="C817" t="inlineStr">
-        <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
-        </is>
-      </c>
-      <c r="D817" t="inlineStr">
-        <is>
-          <t>Forest fire damage assessment - new risks and mitigation</t>
-        </is>
-      </c>
-      <c r="E817" t="inlineStr">
-        <is>
-          <t>POINT (-0.54267 40.01794999999999)</t>
-        </is>
-      </c>
-      <c r="F817" t="inlineStr">
-        <is>
-          <t>2016-06-13T01:00:00</t>
-        </is>
-      </c>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>2026-01-20T09:55:03.938401</t>
-        </is>
-      </c>
-      <c r="H817" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I817" t="b">
-        <v>1</v>
-      </c>
-      <c r="J817" t="n">
-        <v>1</v>
-      </c>
-      <c r="K817" t="n">
-        <v>8</v>
-      </c>
-      <c r="L817" t="inlineStr">
-        <is>
-          <t>Two areas of Special Areas of Conservation: Sierra de Espadn and Curs Alt del riu Millars were hit by a forest fire in July 2015, in the Montn and Caudiel municipalities of the region of Valencia. The analysis of the damage degree and landslide and erosion risk is of key importance for the spatia...</t>
-        </is>
-      </c>
-      <c r="M817" t="inlineStr">
         <is>
           <t>Two areas of Special Areas of Conservation: Sierra de Espadn and Curs Alt del riu Millars were hit by a forest fire in July 2015, in the Montn and Caudiel municipalities of the region of Valencia. The analysis of the damage degree and landslide and erosion risk is of key importance for the spatial and temporal planning of the post-event restoration work. The scope of the activation included:
 Delineation/grading
@@ -46335,6 +46273,68 @@
         </is>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>EMSN025</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Greece'}]</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Forest fire damage assessment – Planning and Recovery</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>POINT (25.579999999999995 38.34999999999999)</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>2016-06-13T01:00:00</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>2026-01-20T09:54:14.348681</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I817" t="b">
+        <v>1</v>
+      </c>
+      <c r="J817" t="n">
+        <v>6</v>
+      </c>
+      <c r="K817" t="n">
+        <v>84</v>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>This activation focuses on damage delineation and grading maps for selected forest fires in Greece in the summer of 2015. Additionally, loss assessment and risk assessment products (landslide/erosion and flash flood) including, mitigation and recovery measures are analysed. Key assets (infrastruc...</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>This activation focuses on damage delineation and grading maps for selected forest fires in Greece in the summer of 2015. Additionally, loss assessment and risk assessment products (landslide/erosion and flash flood) including, mitigation and recovery measures are analysed. Key assets (infrastructure, environment, human life, economic sustainability, etc.) are also identified and related with the probability and severity (impact) of potential (secondary) hazards.
+The activation was triggered  Assets and Trans. Networks at Risk Map - Flood Risk Assessment (Details, Tile 6011) Soil Loss Map - Erosion Hazard Zones (Details, Tile 6011) Assets and Trans. Networks at Risk Map - Landslide Risk Assessment (Details, Tile 6011) Land Use and Land Cover Map - Multiple Natural Hazard Risk Assessment (Details, Tile 6011) Biomass Loss Assessment Map - Fire Damage Assessment (Details, Tile 6011) Delineation and Grading Map - Fire Damage Assessment (Details, Tile 6011) Reference Map - Multiple Natural Hazard Risk Assessment (Details, Tile 6011) Assets and Trans. Networks at Risk Map - Flood Risk Assessment (Details, Tile 5010) Soil Loss Map - Erosion Hazard Zones (Details, Tile 5010) Assets and Trans. Networks at Risk Map - Landslide Risk Assessment (Details, Tile 5010)</t>
+        </is>
+      </c>
+    </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>EMSR085</t>
+          <t>EMSR084</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -51005,17 +51005,17 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'industrial', 'name': 'Industrial Accident'}</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>LuModExercise - Flood in Mertert- Luxembourg</t>
+          <t>LuModExercise - Industrial accident</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>POINT (6.47 49.69)</t>
+          <t>POINT (6.44 49.8)</t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
@@ -51025,7 +51025,7 @@
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>2014-05-28T12:18:00</t>
+          <t>2014-05-30T17:11:00</t>
         </is>
       </c>
       <c r="H899" t="inlineStr">
@@ -51045,14 +51045,14 @@
       <c r="L899" t="inlineStr"/>
       <c r="M899" t="inlineStr">
         <is>
-          <t>Mertert Reference Mertert Reference</t>
+          <t>Echternach Reference Echternach Reference</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>EMSR084</t>
+          <t>EMSR085</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -51062,17 +51062,17 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>{'slug': 'industrial', 'name': 'Industrial Accident'}</t>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>LuModExercise - Industrial accident</t>
+          <t>LuModExercise - Flood in Mertert- Luxembourg</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>POINT (6.44 49.8)</t>
+          <t>POINT (6.47 49.69)</t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
@@ -51082,7 +51082,7 @@
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t>2014-05-30T17:11:00</t>
+          <t>2014-05-28T12:18:00</t>
         </is>
       </c>
       <c r="H900" t="inlineStr">
@@ -51102,7 +51102,7 @@
       <c r="L900" t="inlineStr"/>
       <c r="M900" t="inlineStr">
         <is>
-          <t>Echternach Reference Echternach Reference</t>
+          <t>Mertert Reference Mertert Reference</t>
         </is>
       </c>
     </row>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -9203,7 +9203,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2025-02-18T17:27:34.062042</t>
+          <t>2026-06-24T09:05:32.273818</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="I158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
         <v>1</v>
@@ -9220,7 +9220,11 @@
       <c r="K158" t="n">
         <v>4</v>
       </c>
-      <c r="L158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Risk and Recovery Mapping is activated to support the general Inspectorate for Emergency Situations of Romania and the Romanian Water National Administration in the planning and management of civil protection activities by providing flood risk assessment in the Tazlau river basin.</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
@@ -23304,27 +23308,27 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>EMSN102</t>
+          <t>EMSN103</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Spain'}]</t>
+          <t>[{'short_name': 'Central African Republic'}]</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Wildfires in Huelva, Spain</t>
+          <t>IDP camp monitoring in Bria, Central African Republic</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>POINT (-6.61875 37.43943)</t>
+          <t>POINT (21.9657 6.54857)</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -23345,43 +23349,43 @@
         <v>1</v>
       </c>
       <c r="K415" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d P19-Population displacement location P19-MONIT01-Overview Map P19-Overview Map P19-Population displacement location-MONIT01</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>EMSN103</t>
+          <t>EMSN102</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Central African Republic'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>IDP camp monitoring in Bria, Central African Republic</t>
+          <t>Wildfires in Huelva, Spain</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>POINT (21.9657 6.54857)</t>
+          <t>POINT (-6.61875 37.43943)</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -23402,16 +23406,16 @@
         <v>1</v>
       </c>
       <c r="K416" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d P19-Population displacement location P19-MONIT01-Overview Map P19-Overview Map P19-Population displacement location-MONIT01</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -24567,27 +24571,27 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>EMSN091</t>
+          <t>EMSN093</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Philippines'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
+          <t>{'slug': 'mass', 'name': 'Mass Movement'}</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Assessing changes in subsidence rates in the low Pampanga river basin and Manila area, Philippines</t>
+          <t>Rockfall risk analysis in Valle Gran Rey, La Gomera (Spain)</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>POINT (120.7985 14.78801)</t>
+          <t>POINT (-17.31476 28.102249999999998)</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -24595,10 +24599,14 @@
           <t>2021-04-30T01:00:00</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>2026-01-20T10:00:57.435407</t>
+        </is>
+      </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>recovery</t>
+          <t>preparedness</t>
         </is>
       </c>
       <c r="I437" t="b">
@@ -24608,77 +24616,73 @@
         <v>1</v>
       </c>
       <c r="K437" t="n">
-        <v>1</v>
-      </c>
-      <c r="L437" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering i...</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
-        <is>
-          <t>The service was activated by a request from the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) – authorized user, and the University of Philippines – local user. Several sources suggest that the Manila NCR and lower Pampanga river basin, Philippines, has been affected by ground subsidence phenomena impacting settlements and increasing flood risk.
-The EMS service aims to provide evidence of ground motion Ground Deformation – Overview key map (Overview A1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>EMSN093</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Spain'}]</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>{'slug': 'mass', 'name': 'Mass Movement'}</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>Rockfall risk analysis in Valle Gran Rey, La Gomera (Spain)</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>POINT (-17.31476 28.102249999999998)</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>2021-04-30T01:00:00</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>2026-01-20T10:00:57.435407</t>
-        </is>
-      </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>preparedness</t>
-        </is>
-      </c>
-      <c r="I438" t="b">
-        <v>1</v>
-      </c>
-      <c r="J438" t="n">
-        <v>1</v>
-      </c>
-      <c r="K438" t="n">
-        <v>6</v>
-      </c>
-      <c r="L438" t="inlineStr">
-        <is>
-          <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering i...</t>
-        </is>
-      </c>
-      <c r="M438" t="inlineStr">
         <is>
           <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering information on the potential hazard of the area, to carry out the adequate management plans.
 The products resulting from this activation are:
 Product 2
 Pre-event DEM extracted using photogrammetr Rockfall hazard. Overview key map (Overview A1) Rockfall asset and population risk (low season). Overview key map (Overview A1) Rockfall asset and population risk (high season). Overview key map (Overview A1) Rockfall asset and population exposure. Overview key map (Overview A1) Reference. Overview key map (Overview A1) Ground Deformation. Overview key map (Overview A1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>EMSN091</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Philippines'}]</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Assessing changes in subsidence rates in the low Pampanga river basin and Manila area, Philippines</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>POINT (120.7985 14.78801)</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>2021-04-30T01:00:00</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I438" t="b">
+        <v>1</v>
+      </c>
+      <c r="J438" t="n">
+        <v>1</v>
+      </c>
+      <c r="K438" t="n">
+        <v>1</v>
+      </c>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>The service was activated by a request from the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) – authorized user, and the University of Philippines – local user. Several sources suggest that the Manila NCR and lower Pampanga river basin, Philippines, has been affected by ground subsidence phenomena impacting settlements and increasing flood risk.
+The EMS service aims to provide evidence of ground motion Ground Deformation – Overview key map (Overview A1)</t>
         </is>
       </c>
     </row>
@@ -29924,27 +29928,27 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>EMSN066</t>
+          <t>EMSN071</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Iran'}]</t>
+          <t>[{'short_name': 'Germany'}]</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Flood delineation and flood damage assessment, Iran</t>
+          <t>Wildfires, Preparedness, Arnsberg, Germany</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>POINT (58.96228 25.99307)</t>
+          <t>POINT (8.021859999999998 51.41891999999999)</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
@@ -29952,52 +29956,61 @@
           <t>2020-04-09T01:00:00</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr"/>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>2026-01-20T09:58:16.184451</t>
+        </is>
+      </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>recovery</t>
+          <t>preparedness</t>
         </is>
       </c>
       <c r="I530" t="b">
         <v>1</v>
       </c>
       <c r="J530" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K530" t="n">
-        <v>11</v>
-      </c>
-      <c r="L530" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could...</t>
+        </is>
+      </c>
       <c r="M530" t="inlineStr">
         <is>
-          <t>The scope of the service request EMSN-066 is to delineate the extent and assess damage of 9 to 11 January 2020 flood event, in South-East Iran. As predicted by Copernicus EMS service GloFAS, days of heavy rain from 9 to 11 January 2020 caused severe flooding in southern Iran, in Sistan and Baluchestan, Hormozgan and south of Kerman provinces. Flooding has blocked roads and damaged houses, bridges, crops and infrastructure. Dozens of areas have been left isolated after roads were damaged or block Reservoir and dam change detection (Overview A3) Reference map (Overview A3) Flood delineation (Overview A3) Damage assessment (Overview A3) Reference map (Overview A2) Flood delineation (Overview A2) Damage assessment (Overview A2) Reservoir and dam change detection (Overview A1) Reference map (Overview A1) Flood delineation (Overview A1)</t>
+          <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could hit this territory.
+More than 63% of the town’s area is covered by forest, including several large protected areas; forest plays an important economic role in both tourism and the timber-processing busi Reference map (Overview A1) Land Use Land Cover map (Overview A1) Pre-disaster forest fire hazard (Overview A1) Pre-disaster forest fire exposure (Overview A1)</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>EMSN071</t>
+          <t>EMSN066</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Germany'}]</t>
+          <t>[{'short_name': 'Iran'}]</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Wildfires, Preparedness, Arnsberg, Germany</t>
+          <t>Flood delineation and flood damage assessment, Iran</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>POINT (8.021859999999998 51.41891999999999)</t>
+          <t>POINT (58.96228 25.99307)</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -30005,34 +30018,25 @@
           <t>2020-04-09T01:00:00</t>
         </is>
       </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>2026-01-20T09:58:16.184451</t>
-        </is>
-      </c>
+      <c r="G531" t="inlineStr"/>
       <c r="H531" t="inlineStr">
         <is>
-          <t>preparedness</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I531" t="b">
         <v>1</v>
       </c>
       <c r="J531" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K531" t="n">
-        <v>4</v>
-      </c>
-      <c r="L531" t="inlineStr">
-        <is>
-          <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could...</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="L531" t="inlineStr"/>
       <c r="M531" t="inlineStr">
         <is>
-          <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could hit this territory.
-More than 63% of the town’s area is covered by forest, including several large protected areas; forest plays an important economic role in both tourism and the timber-processing busi Reference map (Overview A1) Land Use Land Cover map (Overview A1) Pre-disaster forest fire hazard (Overview A1) Pre-disaster forest fire exposure (Overview A1)</t>
+          <t>The scope of the service request EMSN-066 is to delineate the extent and assess damage of 9 to 11 January 2020 flood event, in South-East Iran. As predicted by Copernicus EMS service GloFAS, days of heavy rain from 9 to 11 January 2020 caused severe flooding in southern Iran, in Sistan and Baluchestan, Hormozgan and south of Kerman provinces. Flooding has blocked roads and damaged houses, bridges, crops and infrastructure. Dozens of areas have been left isolated after roads were damaged or block Reservoir and dam change detection (Overview A3) Reference map (Overview A3) Flood delineation (Overview A3) Damage assessment (Overview A3) Reference map (Overview A2) Flood delineation (Overview A2) Damage assessment (Overview A2) Reservoir and dam change detection (Overview A1) Reference map (Overview A1) Flood delineation (Overview A1)</t>
         </is>
       </c>
     </row>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -8502,7 +8502,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2024-10-21T08:40:35</t>
+          <t>2026-07-01T15:29:51.136311</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="I158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>1</v>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="I4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>

--- a/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
+++ b/outputs/excel/copernicus_emergency_activities_since_2012.xlsx
@@ -14814,7 +14814,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Kosovo'}]</t>
+          <t>[{'short_name': 'Kosovo*'}]</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Flood in Kosovo</t>
+          <t>Flood in Kosovo*</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -14856,7 +14856,11 @@
       <c r="K261" t="n">
         <v>5</v>
       </c>
-      <c r="L261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Floods occurred on 19th and 20th of January 2023 in northern, eastern and western Kosovo*. The situation has calmed down, but the damages caused by the floods and their consequences remain. The Copernicus Emergency Management Service - Rapid Mapping has been activated in order to estimate the flo...</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr"/>
     </row>
     <row r="262">
@@ -21820,7 +21824,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>EMSN110</t>
+          <t>EMSN109</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -21835,12 +21839,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Wildfire in Alburquerque, Spain</t>
+          <t>Wildfire in Alcaracejos, Spain</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>POINT (-6.85472 40.02093)</t>
+          <t>POINT (-4.94932 38.2282)</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -21870,14 +21874,14 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>EMSN109</t>
+          <t>EMSN108</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -21892,12 +21896,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Wildfire in Alcaracejos, Spain</t>
+          <t>Wildfire in San Felices de los Gallegos, Spain</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>POINT (-4.94932 38.2282)</t>
+          <t>POINT (-6.67526 40.8026)</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -21922,19 +21926,19 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alcaracejos, in the region of Cordoba-Andalucía (Spain), on 16thAugust 2021. According to Infoca Plan, the initial damage assessment resulted in about 610 ha burnt; the fire not only destroye P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>EMSN108</t>
+          <t>EMSN110</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -21949,12 +21953,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Wildfire in San Felices de los Gallegos, Spain</t>
+          <t>Wildfire in Alburquerque, Spain</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>POINT (-6.67526 40.8026)</t>
+          <t>POINT (-6.85472 40.02093)</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -21979,12 +21983,12 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish pro...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the muni...</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Spanish province of Salamanca (Spain), on 17th August 2021. Active flames were located in San Felices de los Gallegos and Bañobrez, as well as in the areas known as La Granja and Los Navazos, on the edge of the Arr P07-Wildfire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the in the municipality of Alburquerque in the region of Badajoz (Spain), on 18thAugust 2021. It spread in different directions, burning cultivated areas, grassland and mountains, until it was extinguished on 22ndAugus P07-Wildfire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -23308,27 +23312,27 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>EMSN103</t>
+          <t>EMSN102</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Central African Republic'}]</t>
+          <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>IDP camp monitoring in Bria, Central African Republic</t>
+          <t>Wildfires in Huelva, Spain</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>POINT (21.9657 6.54857)</t>
+          <t>POINT (-6.61875 37.43943)</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -23349,43 +23353,43 @@
         <v>1</v>
       </c>
       <c r="K415" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d P19-Population displacement location P19-MONIT01-Overview Map P19-Overview Map P19-Population displacement location-MONIT01</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>EMSN102</t>
+          <t>EMSN103</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Spain'}]</t>
+          <t>[{'short_name': 'Central African Republic'}]</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Wildfires in Huelva, Spain</t>
+          <t>IDP camp monitoring in Bria, Central African Republic</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>POINT (-6.61875 37.43943)</t>
+          <t>POINT (21.9657 6.54857)</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -23406,16 +23410,16 @@
         <v>1</v>
       </c>
       <c r="K416" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural are...</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and hum...</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the natural areas of Villarrasa, in the Huelva province (Andalucia region, Southern Spain) on 24th July 2021. A total of 15 aircrafts and 120 forest firefighters fought against the propagation of the wildfire which, ho Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (STD) has been activated by DG ECHO to get updated information about the Internally Displaced Person (IDP) site named PK-3 and located in the proximity of Bria, Central African Republic (CAR). Since 2013, the CAR has been affected by political, security and humanitarian crisis linked to armed conflicts, conflicts between communities, or tensions between farmers and breeders in some areas. This situation of instability in the country has dramatically worsened d P19-Population displacement location P19-MONIT01-Overview Map P19-Overview Map P19-Population displacement location-MONIT01</t>
         </is>
       </c>
     </row>
@@ -23536,7 +23540,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EMSN100</t>
+          <t>EMSN101</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -23551,12 +23555,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Wildfires in La Rioja, Spain</t>
+          <t>Wildfire in Ciudad Real, Spain</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>POINT (-2.01861 42.15347)</t>
+          <t>POINT (-4.85493 38.75007)</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -23581,19 +23585,19 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>EMSN101</t>
+          <t>EMSN100</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -23608,12 +23612,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Wildfire in Ciudad Real, Spain</t>
+          <t>Wildfires in La Rioja, Spain</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>POINT (-4.85493 38.75007)</t>
+          <t>POINT (-2.01861 42.15347)</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -23638,12 +23642,12 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real...</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region...</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in the Ciudad Real province (Castilla la Mancha region, Spain) on 12thJuly 2021. The wildfire hit especially the municipalities of Chillón and Almadén, where about 2000 ha of an agricultural land burnt. The goal of the ac Fire Delineation and Grading</t>
+          <t>The CEMS Risk and Recovery Standard (RRM STD) has been activated by the Spanish General Directorate of Civil Protection and Emergencies (CENEM) on behalf of the Ministry of Interior of Spain, D. G. Guardia Civil and Jefatura del Seprona, following the forest fire that broke out in La Rioja region (North-Eastern Spain) on 18thJuly 2021. Within the municipalities of Autol, Grvalos, Quel and Villarroya more than 200 hectares of wooden areas have burnt. The event affected also more than 360 hectares Fire Delineation and Grading</t>
         </is>
       </c>
     </row>
@@ -24571,118 +24575,118 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
+          <t>EMSN091</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Philippines'}]</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Assessing changes in subsidence rates in the low Pampanga river basin and Manila area, Philippines</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>POINT (120.7985 14.78801)</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>2021-04-30T01:00:00</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I437" t="b">
+        <v>1</v>
+      </c>
+      <c r="J437" t="n">
+        <v>1</v>
+      </c>
+      <c r="K437" t="n">
+        <v>1</v>
+      </c>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>The service was activated by a request from the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) – authorized user, and the University of Philippines – local user. Several sources suggest that the Manila NCR and lower Pampanga river basin, Philippines, has been affected by ground subsidence phenomena impacting settlements and increasing flood risk.
+The EMS service aims to provide evidence of ground motion Ground Deformation – Overview key map (Overview A1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
           <t>EMSN093</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
+      <c r="B438" t="inlineStr">
         <is>
           <t>[{'short_name': 'Spain'}]</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
+      <c r="C438" t="inlineStr">
         <is>
           <t>{'slug': 'mass', 'name': 'Mass Movement'}</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
+      <c r="D438" t="inlineStr">
         <is>
           <t>Rockfall risk analysis in Valle Gran Rey, La Gomera (Spain)</t>
         </is>
       </c>
-      <c r="E437" t="inlineStr">
+      <c r="E438" t="inlineStr">
         <is>
           <t>POINT (-17.31476 28.102249999999998)</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr">
+      <c r="F438" t="inlineStr">
         <is>
           <t>2021-04-30T01:00:00</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr">
+      <c r="G438" t="inlineStr">
         <is>
           <t>2026-01-20T10:00:57.435407</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
+      <c r="H438" t="inlineStr">
         <is>
           <t>preparedness</t>
         </is>
       </c>
-      <c r="I437" t="b">
-        <v>1</v>
-      </c>
-      <c r="J437" t="n">
-        <v>1</v>
-      </c>
-      <c r="K437" t="n">
+      <c r="I438" t="b">
+        <v>1</v>
+      </c>
+      <c r="J438" t="n">
+        <v>1</v>
+      </c>
+      <c r="K438" t="n">
         <v>6</v>
       </c>
-      <c r="L437" t="inlineStr">
+      <c r="L438" t="inlineStr">
         <is>
           <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering i...</t>
         </is>
       </c>
-      <c r="M437" t="inlineStr">
+      <c r="M438" t="inlineStr">
         <is>
           <t>EMSN093 was activated to demonstrate that satellite-derived data can be used to study small-medium sized rockfalls, as the one occurred in Valle Gran Rey of the La Gomera island (Canary Islands, Spain) on the 14thof November 2021. Moreover, the results will support local authorities by offering information on the potential hazard of the area, to carry out the adequate management plans.
 The products resulting from this activation are:
 Product 2
 Pre-event DEM extracted using photogrammetr Rockfall hazard. Overview key map (Overview A1) Rockfall asset and population risk (low season). Overview key map (Overview A1) Rockfall asset and population risk (high season). Overview key map (Overview A1) Rockfall asset and population exposure. Overview key map (Overview A1) Reference. Overview key map (Overview A1) Ground Deformation. Overview key map (Overview A1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>EMSN091</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Philippines'}]</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>Assessing changes in subsidence rates in the low Pampanga river basin and Manila area, Philippines</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>POINT (120.7985 14.78801)</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>2021-04-30T01:00:00</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr"/>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I438" t="b">
-        <v>1</v>
-      </c>
-      <c r="J438" t="n">
-        <v>1</v>
-      </c>
-      <c r="K438" t="n">
-        <v>1</v>
-      </c>
-      <c r="L438" t="inlineStr"/>
-      <c r="M438" t="inlineStr">
-        <is>
-          <t>The service was activated by a request from the Federal Office of Civil Protection and Disaster Assistance (BBK) on behalf of Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ) – authorized user, and the University of Philippines – local user. Several sources suggest that the Manila NCR and lower Pampanga river basin, Philippines, has been affected by ground subsidence phenomena impacting settlements and increasing flood risk.
-The EMS service aims to provide evidence of ground motion Ground Deformation – Overview key map (Overview A1)</t>
         </is>
       </c>
     </row>
@@ -29928,115 +29932,115 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
+          <t>EMSN066</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Iran'}]</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Flood delineation and flood damage assessment, Iran</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>POINT (58.96228 25.99307)</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2020-04-09T01:00:00</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I530" t="b">
+        <v>1</v>
+      </c>
+      <c r="J530" t="n">
+        <v>3</v>
+      </c>
+      <c r="K530" t="n">
+        <v>11</v>
+      </c>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>The scope of the service request EMSN-066 is to delineate the extent and assess damage of 9 to 11 January 2020 flood event, in South-East Iran. As predicted by Copernicus EMS service GloFAS, days of heavy rain from 9 to 11 January 2020 caused severe flooding in southern Iran, in Sistan and Baluchestan, Hormozgan and south of Kerman provinces. Flooding has blocked roads and damaged houses, bridges, crops and infrastructure. Dozens of areas have been left isolated after roads were damaged or block Reservoir and dam change detection (Overview A3) Reference map (Overview A3) Flood delineation (Overview A3) Damage assessment (Overview A3) Reference map (Overview A2) Flood delineation (Overview A2) Damage assessment (Overview A2) Reservoir and dam change detection (Overview A1) Reference map (Overview A1) Flood delineation (Overview A1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
           <t>EMSN071</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B531" t="inlineStr">
         <is>
           <t>[{'short_name': 'Germany'}]</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C531" t="inlineStr">
         <is>
           <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr">
+      <c r="D531" t="inlineStr">
         <is>
           <t>Wildfires, Preparedness, Arnsberg, Germany</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr">
+      <c r="E531" t="inlineStr">
         <is>
           <t>POINT (8.021859999999998 51.41891999999999)</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr">
+      <c r="F531" t="inlineStr">
         <is>
           <t>2020-04-09T01:00:00</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr">
+      <c r="G531" t="inlineStr">
         <is>
           <t>2026-01-20T09:58:16.184451</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
+      <c r="H531" t="inlineStr">
         <is>
           <t>preparedness</t>
         </is>
       </c>
-      <c r="I530" t="b">
-        <v>1</v>
-      </c>
-      <c r="J530" t="n">
-        <v>1</v>
-      </c>
-      <c r="K530" t="n">
+      <c r="I531" t="b">
+        <v>1</v>
+      </c>
+      <c r="J531" t="n">
+        <v>1</v>
+      </c>
+      <c r="K531" t="n">
         <v>4</v>
       </c>
-      <c r="L530" t="inlineStr">
+      <c r="L531" t="inlineStr">
         <is>
           <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could...</t>
         </is>
       </c>
-      <c r="M530" t="inlineStr">
+      <c r="M531" t="inlineStr">
         <is>
           <t>The scope of the service request EMSN-071 is to support the fire department and administration of the City of Arnsberg (Hochsauerland County, State North Rhine-Westphalia, Germany), with designing pre-event preventive measures, as well as incident coordination, in regards of wildfires that could hit this territory.
 More than 63% of the town’s area is covered by forest, including several large protected areas; forest plays an important economic role in both tourism and the timber-processing busi Reference map (Overview A1) Land Use Land Cover map (Overview A1) Pre-disaster forest fire hazard (Overview A1) Pre-disaster forest fire exposure (Overview A1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>EMSN066</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Iran'}]</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>Flood delineation and flood damage assessment, Iran</t>
-        </is>
-      </c>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>POINT (58.96228 25.99307)</t>
-        </is>
-      </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>2020-04-09T01:00:00</t>
-        </is>
-      </c>
-      <c r="G531" t="inlineStr"/>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I531" t="b">
-        <v>1</v>
-      </c>
-      <c r="J531" t="n">
-        <v>3</v>
-      </c>
-      <c r="K531" t="n">
-        <v>11</v>
-      </c>
-      <c r="L531" t="inlineStr"/>
-      <c r="M531" t="inlineStr">
-        <is>
-          <t>The scope of the service request EMSN-066 is to delineate the extent and assess damage of 9 to 11 January 2020 flood event, in South-East Iran. As predicted by Copernicus EMS service GloFAS, days of heavy rain from 9 to 11 January 2020 caused severe flooding in southern Iran, in Sistan and Baluchestan, Hormozgan and south of Kerman provinces. Flooding has blocked roads and damaged houses, bridges, crops and infrastructure. Dozens of areas have been left isolated after roads were damaged or block Reservoir and dam change detection (Overview A3) Reference map (Overview A3) Flood delineation (Overview A3) Damage assessment (Overview A3) Reference map (Overview A2) Flood delineation (Overview A2) Damage assessment (Overview A2) Reservoir and dam change detection (Overview A1) Reference map (Overview A1) Flood delineation (Overview A1)</t>
         </is>
       </c>
     </row>
@@ -30714,27 +30718,27 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>EMSN063</t>
+          <t>EMSN064</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Nigeria'}]</t>
+          <t>[{'short_name': 'Ukraine'}]</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+          <t>{'slug': 'other', 'name': 'Other'}</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Crop change detection in conflict areas, Nigeria</t>
+          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>POINT (12.36791 13.49555)</t>
+          <t>POINT (23.87015 47.95273)</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -30752,74 +30756,74 @@
         <v>1</v>
       </c>
       <c r="J544" t="n">
+        <v>1</v>
+      </c>
+      <c r="K544" t="n">
+        <v>4</v>
+      </c>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>The scope is the assessment of the sinkhole risk in the mining area of Solotvyno, Zakarpattya region, Ukraine, in continuation of the previous serviceEMSN-030. A systematic salt mining began in the second half of the 18th century with up to eight salt mines in operation. Although the flooding with ground water and the erosion of subsoil salt layers began in the early 2000s, the extraction of salt had not been completely stopped until 2010, when in December 3000m³ of land collapsed.
+The aim is t Surface Dynamics Map Subsidence and Landslide Risk Map Reference map Land use/ land cover map</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>EMSN063</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Nigeria'}]</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>{'slug': 'humanitarian', 'name': 'Humanitarian Crisis'}</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Crop change detection in conflict areas, Nigeria</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>POINT (12.36791 13.49555)</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2020-02-14T01:00:00</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I545" t="b">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
         <v>5</v>
       </c>
-      <c r="K544" t="n">
+      <c r="K545" t="n">
         <v>5</v>
       </c>
-      <c r="L544" t="inlineStr">
+      <c r="L545" t="inlineStr">
         <is>
           <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been ac...</t>
         </is>
       </c>
-      <c r="M544" t="inlineStr">
+      <c r="M545" t="inlineStr">
         <is>
           <t>EMSN063 was activated to support the World Food Program in order to provide information about cropland change and population affected by cropland loss in the north-eastern Nigerian Borno region over 5 AOIs, helping to understand the food security situation. The area under focus is has not been accessed for several years and little to no data could be collected due to intense fighting activities by Boko Haram since 2010.
 The aim of the activation is a crop change analysis implemented between the Crop Change Crop Change Crop Change Crop Change Crop Change</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>EMSN064</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Ukraine'}]</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>{'slug': 'other', 'name': 'Other'}</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>Detection and mapping of ground deformations of anthropogenic sinkholes</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>POINT (23.87015 47.95273)</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>2020-02-14T01:00:00</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr"/>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I545" t="b">
-        <v>1</v>
-      </c>
-      <c r="J545" t="n">
-        <v>1</v>
-      </c>
-      <c r="K545" t="n">
-        <v>4</v>
-      </c>
-      <c r="L545" t="inlineStr"/>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>The scope is the assessment of the sinkhole risk in the mining area of Solotvyno, Zakarpattya region, Ukraine, in continuation of the previous serviceEMSN-030. A systematic salt mining began in the second half of the 18th century with up to eight salt mines in operation. Although the flooding with ground water and the erosion of subsoil salt layers began in the early 2000s, the extraction of salt had not been completely stopped until 2010, when in December 3000m³ of land collapsed.
-The aim is t Surface Dynamics Map Subsidence and Landslide Risk Map Reference map Land use/ land cover map</t>
         </is>
       </c>
     </row>
@@ -32812,7 +32816,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>EMSR390</t>
+          <t>EMSR389</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -32827,12 +32831,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Forest fire in Zakynthos Island- Greece</t>
+          <t>Forest fire in Loutraki area- Greece</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>POINT (20.806 37.698)</t>
+          <t>POINT (22.973 37.997)</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -32842,7 +32846,7 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>2019-09-25T11:41:00</t>
+          <t>2019-09-20T13:40:00</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -32859,17 +32863,13 @@
       <c r="K581" t="n">
         <v>2</v>
       </c>
-      <c r="L581" t="inlineStr">
-        <is>
-          <t>A forest fire,  broke out in 15-09-2019 near Lithakia village in Zakynthos Island, 250 Km West from Athens. Fanned by strong winds, this fire forced the evacuation of the villages of Keri and Agalas as a precaution. Copernicus EMS Mapping products will be used for damage assessment, recovery and...</t>
-        </is>
-      </c>
+      <c r="L581" t="inlineStr"/>
       <c r="M581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>EMSR389</t>
+          <t>EMSR390</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -32884,12 +32884,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Forest fire in Loutraki area- Greece</t>
+          <t>Forest fire in Zakynthos Island- Greece</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>POINT (22.973 37.997)</t>
+          <t>POINT (20.806 37.698)</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>2019-09-20T13:40:00</t>
+          <t>2019-09-25T11:41:00</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -32916,7 +32916,11 @@
       <c r="K582" t="n">
         <v>2</v>
       </c>
-      <c r="L582" t="inlineStr"/>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>A forest fire,  broke out in 15-09-2019 near Lithakia village in Zakynthos Island, 250 Km West from Athens. Fanned by strong winds, this fire forced the evacuation of the villages of Keri and Agalas as a precaution. Copernicus EMS Mapping products will be used for damage assessment, recovery and...</t>
+        </is>
+      </c>
       <c r="M582" t="inlineStr"/>
     </row>
     <row r="583">
@@ -33665,7 +33669,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Albania'}, {'short_name': 'Kosovo'}, {'short_name': 'Montenegro'}, {'short_name': 'North Macedonia'}]</t>
+          <t>[{'short_name': 'Albania'}, {'short_name': 'Kosovo*'}, {'short_name': 'Montenegro'}, {'short_name': 'North Macedonia'}]</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -33680,7 +33684,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>POINT (19.975 41.82)</t>
+          <t>POINT (19.975 41.81999999999998)</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
@@ -33688,7 +33692,11 @@
           <t>2019-08-02T01:00:00</t>
         </is>
       </c>
-      <c r="G597" t="inlineStr"/>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>2026-09-04T14:32:32</t>
+        </is>
+      </c>
       <c r="H597" t="inlineStr">
         <is>
           <t>preparedness</t>
@@ -33703,10 +33711,14 @@
       <c r="K597" t="n">
         <v>22</v>
       </c>
-      <c r="L597" t="inlineStr"/>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>* This designation is without prejudice to positions on status and is in line with UNSCR 1244/1999 and the ICJ Opinion on the Kosovo declaration of independence.</t>
+        </is>
+      </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t>The specific activation focuses on deepening the analysis concerning the occurrence of floods within a transboundary AOI that corresponds to the Drin catchment area and more specifically to the part that extends into four countries, namely Albania, Kosovo, the Former Yugoslavian Republic of Macedonia and Montenegro.
+          <t>The specific activation focuses on deepening the analysis concerning the occurrence of floods within a transboundary AOI that corresponds to the Drin catchment area and more specifically to the part that extends into four countries, namely Albania, Kosovo*, the Former Yugoslavian Republic of Macedonia and Montenegro.
 The service and the products aim to serve the scope of the Drin River Cooperation agreement on sustainable management of water resources in the Drin catchment area through providi Reference Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 10/1992 (Bar, Cetinje, Podgorica, Shkodra, Ulcinj) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 08/1995 (Bar, Cetinje, Lezhe, Podgorica, Shkodra, Ulcinj) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Economic Assets map - Critical Infrastructures Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 10/2002 (Bar, Lezhe, Podgorica, Shkodra, Ulcinj) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 12/2004 (Bar, Cetinje, Danilovgrad, Niksic, Podgorica, Shkodra) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment (Drin Basin (11-2007)) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 12/2009 - 01/2010 (Basin Area) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 11,12/2010 (Bar, Cetinje, Lezhe, Podgorica, Shkodra, Ulcinj) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact Historical Analysis - Maximum Flood Extent and Damages Assessment, 03,04/2013 (Basin Area) Map - Drin River Basin - Assessment of Flood risk &amp; Economic impact</t>
         </is>
       </c>
@@ -44911,117 +44923,117 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
+          <t>EMSN032</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>[{'short_name': 'Portugal'}]</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Forest fire damage assessment, Portugal</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>POINT (-8.21612 40.898399999999995)</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>2016-10-17T01:00:00</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>2026-01-20T09:56:25.083357</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="I793" t="b">
+        <v>1</v>
+      </c>
+      <c r="J793" t="n">
+        <v>1</v>
+      </c>
+      <c r="K793" t="n">
+        <v>120</v>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>The scope of the service request EMSN032 is to generate damage delineation and grading maps of 41 different forest fires in mainland Portugal that occurred in July and August 2016. The affected area had an overall extent of 887 km².
+The service consists of detailed reference maps and damage de...</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>The scope of the service request EMSN032 is to generate damage delineation and grading maps of 41 different forest fires in mainland Portugal that occurred in July and August 2016. The affected area had an overall extent of 887 km².
+The service consists of detailed reference maps and damage delineation and grading. Additionally, assessment of post-event slope stability, erosion and accessibility to the affected areas were requested. All layers were produced at the cartographic scale of 1:25,0 Reference map Assessment of Access Erosion Risk Fire Delineation and Grading Landslide Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
           <t>EMSN030</t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>[{'short_name': 'Ukraine'}]</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>{'slug': 'other', 'name': 'Other'}</t>
         </is>
       </c>
-      <c r="D793" t="inlineStr">
+      <c r="D794" t="inlineStr">
         <is>
           <t>Ground deformation mapping and monitoring by satellite based multi-temporal DInSAR technique</t>
         </is>
       </c>
-      <c r="E793" t="inlineStr">
+      <c r="E794" t="inlineStr">
         <is>
           <t>POINT (23.86 47.95)</t>
         </is>
       </c>
-      <c r="F793" t="inlineStr">
+      <c r="F794" t="inlineStr">
         <is>
           <t>2016-10-17T01:00:00</t>
         </is>
       </c>
-      <c r="G793" t="inlineStr"/>
-      <c r="H793" t="inlineStr">
+      <c r="G794" t="inlineStr"/>
+      <c r="H794" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="I793" t="b">
-        <v>1</v>
-      </c>
-      <c r="J793" t="n">
-        <v>1</v>
-      </c>
-      <c r="K793" t="n">
+      <c r="I794" t="b">
+        <v>1</v>
+      </c>
+      <c r="J794" t="n">
+        <v>1</v>
+      </c>
+      <c r="K794" t="n">
         <v>40</v>
       </c>
-      <c r="L793" t="inlineStr"/>
-      <c r="M793" t="inlineStr">
+      <c r="L794" t="inlineStr"/>
+      <c r="M794" t="inlineStr">
         <is>
           <t>EMSN030 was activated by the National Directorate General for Disaster Management, Hungary, on behalf of the EUCPT (Scoping Mission in Solotvyno salt mine, Ukraine) on 12/7/2016. The crisis related to the structural deterioration of old salt mines due to flooding of mine shafts and subsequent contamination of the Tisza River. Underground cavities and sinkholes emerged, threatening the local population, as well as industrial buildings and engineering systems.
 In order to monitor the ground def Current Trends Map - Sinkhole and Landslides Risk Map Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1004) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1003) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1002) Current Trends Map - Sinkhole and Landslides Risk Map (Details, Tile 1001) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1004) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1003) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1002) Current Trends, Period: 2016-2017 Map - Ground Deformation Dynamics (Details, Tile 1001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
-        <is>
-          <t>EMSN032</t>
-        </is>
-      </c>
-      <c r="B794" t="inlineStr">
-        <is>
-          <t>[{'short_name': 'Portugal'}]</t>
-        </is>
-      </c>
-      <c r="C794" t="inlineStr">
-        <is>
-          <t>{'slug': 'fire', 'name': 'Wildfire'}</t>
-        </is>
-      </c>
-      <c r="D794" t="inlineStr">
-        <is>
-          <t>Forest fire damage assessment, Portugal</t>
-        </is>
-      </c>
-      <c r="E794" t="inlineStr">
-        <is>
-          <t>POINT (-8.21612 40.898399999999995)</t>
-        </is>
-      </c>
-      <c r="F794" t="inlineStr">
-        <is>
-          <t>2016-10-17T01:00:00</t>
-        </is>
-      </c>
-      <c r="G794" t="inlineStr">
-        <is>
-          <t>2026-01-20T09:56:25.083357</t>
-        </is>
-      </c>
-      <c r="H794" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="I794" t="b">
-        <v>1</v>
-      </c>
-      <c r="J794" t="n">
-        <v>1</v>
-      </c>
-      <c r="K794" t="n">
-        <v>120</v>
-      </c>
-      <c r="L794" t="inlineStr">
-        <is>
-          <t>The scope of the service request EMSN032 is to generate damage delineation and grading maps of 41 different forest fires in mainland Portugal that occurred in July and August 2016. The affected area had an overall extent of 887 km².
-The service consists of detailed reference maps and damage de...</t>
-        </is>
-      </c>
-      <c r="M794" t="inlineStr">
-        <is>
-          <t>The scope of the service request EMSN032 is to generate damage delineation and grading maps of 41 different forest fires in mainland Portugal that occurred in July and August 2016. The affected area had an overall extent of 887 km².
-The service consists of detailed reference maps and damage delineation and grading. Additionally, assessment of post-event slope stability, erosion and accessibility to the affected areas were requested. All layers were produced at the cartographic scale of 1:25,0 Reference map Assessment of Access Erosion Risk Fire Delineation and Grading Landslide Risk</t>
         </is>
       </c>
     </row>
@@ -51402,12 +51414,12 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>EMSN040</t>
+          <t>EMSN024</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Finland'}]</t>
+          <t>[{'short_name': 'Germany'}]</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -51417,12 +51429,12 @@
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Basic European Assets Map, Finland</t>
+          <t>Basic European Assets Map, Germany</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>POINT (25.74815 61.92411)</t>
+          <t>POINT (10.44768 51.16338)</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
@@ -51448,19 +51460,19 @@
       <c r="L906" t="inlineStr"/>
       <c r="M906" t="inlineStr">
         <is>
-          <t>Service Request: The nation-wide asset mapping for Finland provides a detailed regional geospatial dataset for the quick and uncomplicated calculation of potential damages either in the preparedness phase or during the immediate response phase of crises caused by natural hazard events. The concept follows the Basic European Asset Map (BEAM) data model developed under the Copernicus precursor project SAFER (Services and Applications for Emergency Response) and extended in the FP7 project IncREO ( BEAM V2 2012 Finland</t>
+          <t>Risk analysis for natural hazard topics, damage assessment Asset Map Germany</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>EMSN024</t>
+          <t>EMSN040</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Germany'}]</t>
+          <t>[{'short_name': 'Finland'}]</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -51470,12 +51482,12 @@
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Basic European Assets Map, Germany</t>
+          <t>Basic European Assets Map, Finland</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>POINT (10.44768 51.16338)</t>
+          <t>POINT (25.74815 61.92411)</t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
@@ -51501,7 +51513,7 @@
       <c r="L907" t="inlineStr"/>
       <c r="M907" t="inlineStr">
         <is>
-          <t>Risk analysis for natural hazard topics, damage assessment Asset Map Germany</t>
+          <t>Service Request: The nation-wide asset mapping for Finland provides a detailed regional geospatial dataset for the quick and uncomplicated calculation of potential damages either in the preparedness phase or during the immediate response phase of crises caused by natural hazard events. The concept follows the Basic European Asset Map (BEAM) data model developed under the Copernicus precursor project SAFER (Services and Applications for Emergency Response) and extended in the FP7 project IncREO ( BEAM V2 2012 Finland</t>
         </is>
       </c>
     </row>
@@ -53230,27 +53242,27 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>EMSN005</t>
+          <t>EMSN006</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Austria'}]</t>
+          <t>[{'short_name': 'Czechia'}]</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>{'slug': 'flood', 'name': 'Flood'}</t>
+          <t>{'slug': 'storm', 'name': 'Storm'}</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>EU Civil Protection Exercise: EU TARANIS 2013</t>
+          <t>Civil Protection Exercise: RESTART 2013</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>POINT (13.06265 47.81082)</t>
+          <t>POINT (15.9473 49.95137)</t>
         </is>
       </c>
       <c r="F938" t="inlineStr">
@@ -53268,42 +53280,42 @@
         <v>1</v>
       </c>
       <c r="J938" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K938" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L938" t="inlineStr"/>
       <c r="M938" t="inlineStr">
         <is>
-          <t>Delineation Map (Detail 3) Delineation Map Delineation Map (Detail 2) Delineation Map (Detail 1) Reference Map (Detail 3) Reference Map (Detail 2) Reference Map (Detail 1) Reference Map</t>
+          <t>Delineation Map Reference Map Reference Map Reference Map Delineation Map (Detail 5) Delineation Map (Detail 4) Delineation Map (Detail 2) Delineation Map (Detail 1) Delineation Map  Reference Map  (Detail 5)</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>EMSN006</t>
+          <t>EMSN005</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>[{'short_name': 'Czechia'}]</t>
+          <t>[{'short_name': 'Austria'}]</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>{'slug': 'storm', 'name': 'Storm'}</t>
+          <t>{'slug': 'flood', 'name': 'Flood'}</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>Civil Protection Exercise: RESTART 2013</t>
+          <t>EU Civil Protection Exercise: EU TARANIS 2013</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>POINT (15.9473 49.95137)</t>
+          <t>POINT (13.06265 47.81082)</t>
         </is>
       </c>
       <c r="F939" t="inlineStr">
@@ -53321,15 +53333,15 @@
         <v>1</v>
       </c>
       <c r="J939" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K939" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L939" t="inlineStr"/>
       <c r="M939" t="inlineStr">
         <is>
-          <t>Delineation Map Reference Map Reference Map Reference Map Delineation Map (Detail 5) Delineation Map (Detail 4) Delineation Map (Detail 2) Delineation Map (Detail 1) Delineation Map  Reference Map  (Detail 5)</t>
+          <t>Delineation Map (Detail 3) Delineation Map Delineation Map (Detail 2) Delineation Map (Detail 1) Reference Map (Detail 3) Reference Map (Detail 2) Reference Map (Detail 1) Reference Map</t>
         </is>
       </c>
     </row>
